--- a/CBT_2025_2회/산업안전기사_2025_2회_문항등록.xlsx
+++ b/CBT_2025_2회/산업안전기사_2025_2회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="AI8" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;보호구 안전인증 고시 — 안전모의 시험성능기준&lt;/strong&gt;&lt;br&gt;숫자로 잡아 둔다 — &lt;strong&gt;내관통성 AE·ABE 는 관통거리 9.5 [mm] 이하, AB 는 11.1 [mm] 이하&lt;/strong&gt;, &lt;strong&gt;충격흡수성은 전달충격력 4,450 [N] 미만&lt;/strong&gt;, &lt;strong&gt;내전압성은 교류 20 [kV] 에서 1분간 누설전류 10 [mA] 이하&lt;/strong&gt;, &lt;strong&gt;내수성은 질량증가율 1 [%] 미만&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내열성은 없다&lt;/u&gt; — 난연성과 헷갈리지 말 것.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;보호구 안전인증 고시 — 안전모의 시험성능기준&lt;/strong&gt;&lt;br&gt;숫자로 잡아 둔다 — &lt;strong&gt;내관통성 AE·ABE는 관통거리 9.5 [mm] 이하, AB는 11.1 [mm] 이하&lt;/strong&gt;, &lt;strong&gt;충격흡수성은 전달충격력 4,450 [N] 미만&lt;/strong&gt;, &lt;strong&gt;내전압성은 교류 20 [kV]에서 1분간 누설전류 10 [mA] 이하&lt;/strong&gt;, &lt;strong&gt;내수성은 질량증가율 1 [%] 미만&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내열성은 없다&lt;/u&gt; — 난연성과 헷갈리지 말 것.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AI10" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;생체리듬(biorhythm)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;각 리듬이 (+)에서 (−)로 넘어가는 날&lt;/strong&gt;을 &lt;strong&gt;위험일&lt;/strong&gt;이라 하며, 한 달에 약 6일쯤 온다. &lt;strong&gt;세 리듬이 겹치는 날이 가장 위험&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;23 육체 · 28 감성 · 33 지성&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;생체리듬(biorhythm)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;각 리듬이 (+)에서 (−)로 넘어가는 날&lt;/strong&gt;을 &lt;strong&gt;위험일&lt;/strong&gt;이라 하며, 한 달에 약 6일쯤 온다. &lt;strong&gt;세 리듬이 겹치는 날이 가장 위험&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;23 육체 · 28 감성 · 33 지성&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2886,17 +2886,17 @@
       </c>
       <c r="AG14" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;다수에게 조직적으로 가르치는 것&lt;/strong&gt;은 &lt;strong&gt;Off.J.T&lt;/strong&gt;의 장점이다. O.J.T 는 개별 또는 소수 지도다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;O.J.T 와 Off.J.T&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;O.J.T&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off.J.T&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일터를 떠나 한자리에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가 가르치나&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;외부 전문가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;인원&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개별 · 소수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다수 동시&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;맞춤&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개인과 직장 실정에 맞춘다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;일률적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;업무&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끊기지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;끊긴다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;시설·교재&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제한적&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 시설을 쓴다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;다수에게 조직적으로 가르치는 것&lt;/strong&gt;은 &lt;strong&gt;Off.J.T&lt;/strong&gt;의 장점이다. O.J.T는 개별 또는 소수 지도다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;O.J.T와 Off.J.T&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;O.J.T&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off.J.T&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일터를 떠나 한자리에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가 가르치나&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;외부 전문가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;인원&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개별 · 소수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다수 동시&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;맞춤&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개인과 직장 실정에 맞춘다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;일률적&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;업무&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끊기지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;끊긴다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;시설·교재&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제한적&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 시설을 쓴다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH14" s="32" t="inlineStr">
         <is>
-          <t>② 직장 실정에 맞는 실제적 훈련은 O.J.T 의 장점이다.&lt;br&gt;③ 업무의 지속성이 유지되는 것도 O.J.T 다.&lt;br&gt;④ 직속상사에 의한 교육도 O.J.T 다.</t>
+          <t>② 직장 실정에 맞는 실제적 훈련은 O.J.T의 장점이다.&lt;br&gt;③ 업무의 지속성이 유지되는 것도 O.J.T다.&lt;br&gt;④ 직속상사에 의한 교육도 O.J.T다.</t>
         </is>
       </c>
       <c r="AI14" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;O.J.T(직장 내 교육)와 Off.J.T(직장 외 교육)&lt;/strong&gt;&lt;br&gt;가르는 물음 — &lt;strong&gt;일을 하면서 배우는가&lt;/strong&gt;. &lt;strong&gt;「다수」·「전문가」·「전문 시설」이 보이면 Off.J.T&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;O.J.T 는 개별·계속, Off.J.T 는 다수·전문&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;O.J.T(직장 내 교육)와 Off.J.T(직장 외 교육)&lt;/strong&gt;&lt;br&gt;가르는 물음 — &lt;strong&gt;일을 하면서 배우는가&lt;/strong&gt;. &lt;strong&gt;「다수」·「전문가」·「전문 시설」이 보이면 Off.J.T&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;O.J.T는 개별·계속, Off.J.T는 다수·전문&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AG15" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;버즈세션&lt;/strong&gt;이다. &lt;strong&gt;6명이 6분간&lt;/strong&gt; 토의한다 하여 &lt;strong&gt;6-6 회의&lt;/strong&gt;라 부른다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;집단 토의 기법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;어떻게 하나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버즈세션&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6명씩 나눠 6분간&lt;/u&gt; 토의한 뒤 종합&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6-6 회의&lt;/u&gt; — 전원이 말한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;포럼&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;먼저 자료나 사례를 제시&lt;/u&gt; 하고 청중이 질문·토의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;청중 참여가 크다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;심포지엄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;여러 강사가 &lt;u&gt;주제를 나눠 발표&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전문가 중심&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;패널 디스커션&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;패널끼리 토의&lt;/u&gt; 한 뒤 청중과 질의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4~5명&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;케이스 메소드&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사례를 주고 스스로 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사례연구법&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;버즈세션&lt;/strong&gt;이다. &lt;strong&gt;6명이 6분간&lt;/strong&gt; 토의한다 하여 &lt;strong&gt;6-6 회의&lt;/strong&gt;라 부른다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;집단 토의 기법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기법&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;어떻게 하나&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버즈세션&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6명씩 나눠 6분간&lt;/u&gt; 토의한 뒤 종합&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6-6 회의&lt;/u&gt; — 전원이 말한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;포럼&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;먼저 자료나 사례를 제시&lt;/u&gt;하고 청중이 질문·토의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;청중 참여가 크다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;심포지엄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;여러 강사가 &lt;u&gt;주제를 나눠 발표&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전문가 중심&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;패널 디스커션&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;패널끼리 토의&lt;/u&gt;한 뒤 청중과 질의&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4~5명&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;케이스 메소드&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사례를 주고 스스로 분석&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사례연구법&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH15" s="32" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="AG22" s="32" t="inlineStr">
         <is>
-          <t>강도율은 $\dfrac{\text{근로손실일수}}{\text{연근로시간}} \times 1 {,} 000$ 이므로 &lt;strong&gt;근로시간 1,000시간당 근로손실일수&lt;/strong&gt;를 뜻한다. &lt;strong&gt;「건수」가 아니라 「일수」&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해 지표가 뜻하는 것&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지표&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 뜻하나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율(FR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{재해건수} / \text{연근로시간} \times 10^{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100만 시간당 재해 건수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율(SR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{근로손실일수} / \text{연근로시간} \times 10^{3}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000시간당 근로손실 일수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연천인율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{재해자수} / \text{평균근로자수} \times 1 {,} 000$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근로자 1,000명당 재해자 수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_02_020_exp1.png"&gt;&lt;em&gt;도수율과 강도율 — 곱하는 수가 다르다&lt;/em&gt;</t>
+          <t>강도율은 $\dfrac{\text{근로손실일수}}{\text{연근로시간}} \times 1 {,} 000$이므로 &lt;strong&gt;근로시간 1,000시간당 근로손실일수&lt;/strong&gt;를 뜻한다. &lt;strong&gt;「건수」가 아니라 「일수」&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해 지표가 뜻하는 것&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지표&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 뜻하나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;도수율(FR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{재해건수} / \text{연근로시간} \times 10^{6}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100만 시간당 재해 건수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율(SR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{근로손실일수} / \text{연근로시간} \times 10^{3}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000시간당 근로손실 일수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연천인율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\text{재해자수} / \text{평균근로자수} \times 1 {,} 000$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근로자 1,000명당 재해자 수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_02_020_exp1.png"&gt;&lt;em&gt;도수율과 강도율 — 곱하는 수가 다르다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH22" s="32" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;배타적 OR 게이트&lt;/strong&gt;다. &lt;strong&gt;둘 이상이 겹치면 출력이 나오지 않는다&lt;/strong&gt;는 조건이 붙는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 수정게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배타적 OR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 둘 이상 겹치면 출력이 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;「동시 발생이 없음」&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조합 AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 n 개 가운데 k 개가 일어나면 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;「어느 것이든 2개」&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건이 만족될 때만&lt;/u&gt; 출력&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수정기호를 안에 넣는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우선적 AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 순서대로&lt;/u&gt; 일어나야 출력&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험지속 기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 일정 시간 이어져야&lt;/u&gt; 출력&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;배타적 OR 게이트&lt;/strong&gt;다. &lt;strong&gt;둘 이상이 겹치면 출력이 나오지 않는다&lt;/strong&gt;는 조건이 붙는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 수정게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배타적 OR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 둘 이상 겹치면 출력이 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;「동시 발생이 없음」&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조합 AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 n 개 가운데 k 개가 일어나면 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;「어느 것이든 2개」&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건이 만족될 때만&lt;/u&gt; 출력&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수정기호를 안에 넣는다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우선적 AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 순서대로&lt;/u&gt; 일어나야 출력&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험지속 기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 일정 시간 이어져야&lt;/u&gt; 출력&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="AI23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 수정게이트&lt;/strong&gt;&lt;br&gt;수정게이트는 &lt;strong&gt;AND 나 OR 에 조건을 덧붙인 것&lt;/strong&gt;이다. 육각형 안에 조건을 적어 옆에 매단다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;동시에 겹치면 안 되면 배타적 OR&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항은 가답안이 ②였으나 &lt;u&gt;확정답안에서 전항 정답 처리&lt;/u&gt; 되었다. &lt;u&gt;「부정 OR」·「조합 OR」 같은 보기 이름이 표준 용어가 아니어서&lt;/u&gt; 보기 구성이 명확하지 않았기 때문이다. 개념 자체는 &lt;u&gt;배타적 OR 게이트&lt;/u&gt;로 익혀 두면 된다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 수정게이트&lt;/strong&gt;&lt;br&gt;수정게이트는 &lt;strong&gt;AND 나 OR에 조건을 덧붙인 것&lt;/strong&gt;이다. 육각형 안에 조건을 적어 옆에 매단다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;동시에 겹치면 안 되면 배타적 OR&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 원본 문항은 가답안이 ②였으나 &lt;u&gt;확정답안에서 전항 정답 처리&lt;/u&gt; 되었다. &lt;u&gt;「부정 OR」·「조합 OR」 같은 보기 이름이 표준 용어가 아니어서&lt;/u&gt; 보기 구성이 명확하지 않았기 때문이다. 개념 자체는 &lt;u&gt;배타적 OR 게이트&lt;/u&gt;로 익혀 두면 된다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;제2단계는 사상마다 재해원인을 규명&lt;/strong&gt; 하는 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 에 의한 재해사례 연구순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱 사상의 선정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;무엇을 막을 것인가 정한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사상마다 재해원인을 규명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상사상과 중간사상의 원인&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FT 도의 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;앞에서 캔 원인을 그림으로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개선계획의 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대책 수립&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개선계획의 실시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;제2단계는 사상마다 재해원인을 규명&lt;/strong&gt;하는 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA에 의한 재해사례 연구순서&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;톱 사상의 선정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;무엇을 막을 것인가 정한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사상마다 재해원인을 규명&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상사상과 중간사상의 원인&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FT 도의 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;앞에서 캔 원인을 그림으로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개선계획의 작성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대책 수립&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개선계획의 실시&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 에 의한 재해사례 연구순서&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;무엇을 막을지 정하고(1) → 왜 일어나는지 캐고(2) → 그림으로 그리고(3) → 대책을 세워(4) → 실행한다(5)&lt;/strong&gt;. &lt;strong&gt;FT 도를 먼저 그리는 것이 아니라 원인을 먼저 캔다&lt;/strong&gt;는 순서가 핵심이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;톱 → 원인 → FT도 → 계획 → 실시&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA에 의한 재해사례 연구순서&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;무엇을 막을지 정하고(1) → 왜 일어나는지 캐고(2) → 그림으로 그리고(3) → 대책을 세워(4) → 실행한다(5)&lt;/strong&gt;. &lt;strong&gt;FT 도를 먼저 그리는 것이 아니라 원인을 먼저 캔다&lt;/strong&gt;는 순서가 핵심이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;톱 → 원인 → FT도 → 계획 → 실시&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="AI27" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인간 전달함수(Human Transfer Function)&lt;/strong&gt;&lt;br&gt;인간 전달함수는 &lt;strong&gt;사람의 반응을 수식으로 모형화&lt;/strong&gt; 한 것이다. 결점 셋은 모두 &lt;strong&gt;실제 사람을 다 담아내지 못한다&lt;/strong&gt;는 한 가지를 가리킨다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;입력 협소 · 시점 제약 · 직무 묘사 불충분&lt;/u&gt; 셋.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인간 전달함수(Human Transfer Function)&lt;/strong&gt;&lt;br&gt;인간 전달함수는 &lt;strong&gt;사람의 반응을 수식으로 모형화&lt;/strong&gt;한 것이다. 결점 셋은 모두 &lt;strong&gt;실제 사람을 다 담아내지 못한다&lt;/strong&gt;는 한 가지를 가리킨다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;입력 협소 · 시점 제약 · 직무 묘사 불충분&lt;/u&gt; 셋.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;「고장의 영향크기」&lt;/strong&gt;라는 평가요소는 없다. 다섯 요소는 &lt;strong&gt;기능적 고장 영향의 중요도 · 영향을 미치는 시스템의 범위 · 고장발생의 빈도 · 고장방지의 가능성 · 신규 설계의 정도&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA 의 다섯 평가요소&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;평가요소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 보나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기능적 고장 영향의 중요도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;그 고장이 기능에 얼마나 치명적인가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영향을 미치는 시스템의 범위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;어디까지 번지는가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장발생의 빈도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;얼마나 자주 나는가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장방지의 가능성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;막을 수 있는가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신규 설계의 정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;검증되지 않은 새 설계인가&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;「고장의 영향크기」&lt;/strong&gt;라는 평가요소는 없다. 다섯 요소는 &lt;strong&gt;기능적 고장 영향의 중요도 · 영향을 미치는 시스템의 범위 · 고장발생의 빈도 · 고장방지의 가능성 · 신규 설계의 정도&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA의 다섯 평가요소&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;평가요소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 보나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기능적 고장 영향의 중요도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;그 고장이 기능에 얼마나 치명적인가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영향을 미치는 시스템의 범위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;어디까지 번지는가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장발생의 빈도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;얼마나 자주 나는가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장방지의 가능성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;막을 수 있는가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신규 설계의 정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;검증되지 않은 새 설계인가&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="AI30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FMEA 의 평가요소&lt;/strong&gt;&lt;br&gt;FMEA 는 &lt;strong&gt;귀납적·정성적&lt;/strong&gt;이며 &lt;strong&gt;아래에서 위로&lt;/strong&gt; 올라간다. &lt;strong&gt;치명도까지 숫자로 매기면 CA&lt;/strong&gt;이고, 둘을 합친 것이 &lt;strong&gt;FMECA&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;중요도 · 범위 · 빈도 · 방지 가능성 · 신규 설계&lt;/u&gt; 다섯.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FMEA의 평가요소&lt;/strong&gt;&lt;br&gt;FMEA는 &lt;strong&gt;귀납적·정성적&lt;/strong&gt;이며 &lt;strong&gt;아래에서 위로&lt;/strong&gt; 올라간다. &lt;strong&gt;치명도까지 숫자로 매기면 CA&lt;/strong&gt;이고, 둘을 합친 것이 &lt;strong&gt;FMECA&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;중요도 · 범위 · 빈도 · 방지 가능성 · 신규 설계&lt;/u&gt; 다섯.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시스템 수명주기와 위험분석 기법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;단계마다 알맞은 분석기법&lt;/strong&gt;이 있다. &lt;strong&gt;PHA 는 맨 처음(구상단계)&lt;/strong&gt;에 하는 것이 특징이라 「예비(preliminary)」라는 이름이 붙었다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;구 · 정 · 개 · 생 · 운&lt;/u&gt; — 운전이 마지막.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;시스템 수명주기와 위험분석 기법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;단계마다 알맞은 분석기법&lt;/strong&gt;이 있다. &lt;strong&gt;PHA는 맨 처음(구상단계)&lt;/strong&gt;에 하는 것이 특징이라 「예비(preliminary)」라는 이름이 붙었다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;구 · 정 · 개 · 생 · 운&lt;/u&gt; — 운전이 마지막.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5204,17 +5204,17 @@
       </c>
       <c r="AG32" s="32" t="inlineStr">
         <is>
-          <t>$A = \dfrac{\mathrm{MTBF}}{\mathrm{MTBF} + \mathrm{MTTR}}$ 다. $0.9 = \dfrac{\mathrm{MTBF}}{\mathrm{MTBF} + 2}$ 이므로 $0.9 \mathrm{MTBF} + 1.8 = \mathrm{MTBF}$, $0.1 \mathrm{MTBF} = 1.8$, $\mathrm{MTBF} = 18$ 시간이다.&lt;img src="safe_A_2025_02_030_exp1.png"&gt;&lt;em&gt;MTBF · MTTF · MTTR 의 관계&lt;/em&gt;</t>
+          <t>$A = \dfrac{\mathrm{MTBF}}{\mathrm{MTBF} + \mathrm{MTTR}}$다. $0.9 = \dfrac{\mathrm{MTBF}}{\mathrm{MTBF} + 2}$이므로 $0.9 \mathrm{MTBF} + 1.8 = \mathrm{MTBF}$, $0.1 \mathrm{MTBF} = 1.8$, $\mathrm{MTBF} = 18$ 시간이다.&lt;img src="safe_A_2025_02_030_exp1.png"&gt;&lt;em&gt;MTBF · MTTF · MTTR의 관계&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH32" s="32" t="inlineStr">
         <is>
-          <t>① 15시간이면 가용도가 0.882 다.&lt;br&gt;② 16시간이면 0.889 다.&lt;br&gt;③ 17시간이면 0.895 다.</t>
+          <t>① 15시간이면 가용도가 0.882다.&lt;br&gt;② 16시간이면 0.889다.&lt;br&gt;③ 17시간이면 0.895다.</t>
         </is>
       </c>
       <c r="AI32" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가용도(availability)&lt;/strong&gt;&lt;br&gt;$A = \dfrac{\mathrm{MTBF}}{\mathrm{MTBF} + \mathrm{MTTR}} = \dfrac{\mathrm{MTBF}}{\mathrm{MTTF} + \mathrm{MTTR}}$ 다. &lt;strong&gt;전체 시간 가운데 쓸 수 있는 시간의 비율&lt;/strong&gt;을 뜻한다. &lt;strong&gt;MTBF = MTTF + MTTR&lt;/strong&gt;이라는 관계도 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $A = \mathrm{MTBF} \div ( \mathrm{MTBF} + \mathrm{MTTR} )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;가용도(availability)&lt;/strong&gt;&lt;br&gt;$A = \dfrac{\mathrm{MTBF}}{\mathrm{MTBF} + \mathrm{MTTR}} = \dfrac{\mathrm{MTBF}}{\mathrm{MTTF} + \mathrm{MTTR}}$다. &lt;strong&gt;전체 시간 가운데 쓸 수 있는 시간의 비율&lt;/strong&gt;을 뜻한다. &lt;strong&gt;MTBF = MTTF + MTTR&lt;/strong&gt;이라는 관계도 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $A = \mathrm{MTBF} \div ( \mathrm{MTBF} + \mathrm{MTTR} )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;우발고장기간은 고장률이 낮고 일정&lt;/strong&gt; 하다. 그래서 &lt;strong&gt;일정형(CFR)&lt;/strong&gt;이라 부르며, 이 구간이 &lt;strong&gt;설비의 실제 사용 기간&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;욕조곡선의 세 구간&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;고장률&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원인&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;초기고장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소형(DFR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계·제조 결함&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;번인 · 디버깅 · 스크리닝&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우발고장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일정형(CFR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;우연한 과부하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;예비품 준비&lt;/u&gt; · 안전계수 확보&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;마모고장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;증가형(IFR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부식 · 산화 · 마모 · 노화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;예방보전(PM)&lt;/u&gt; · 정기 교체&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_02_031_exp1.png"&gt;&lt;em&gt;욕조곡선 — 구간마다 대책이 다르다&lt;/em&gt;</t>
+          <t>&lt;strong&gt;우발고장기간은 고장률이 낮고 일정&lt;/strong&gt;하다. 그래서 &lt;strong&gt;일정형(CFR)&lt;/strong&gt;이라 부르며, 이 구간이 &lt;strong&gt;설비의 실제 사용 기간&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;욕조곡선의 세 구간&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;고장률&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원인&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;초기고장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감소형(DFR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계·제조 결함&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;번인 · 디버깅 · 스크리닝&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우발고장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일정형(CFR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;우연한 과부하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;예비품 준비&lt;/u&gt; · 안전계수 확보&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;마모고장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;증가형(IFR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부식 · 산화 · 마모 · 노화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;예방보전(PM)&lt;/u&gt; · 정기 교체&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_02_031_exp1.png"&gt;&lt;em&gt;욕조곡선 — 구간마다 대책이 다르다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
@@ -5720,12 +5720,12 @@
       </c>
       <c r="AG36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;레이노 병&lt;/strong&gt;이다. &lt;strong&gt;손가락이 하얗게 질린다&lt;/strong&gt; 하여 &lt;strong&gt;백랍병(白蠟病)&lt;/strong&gt; 이라고도 한다. 착암기·그라인더 같은 &lt;strong&gt;진동공구&lt;/strong&gt;를 오래 쓰면 생긴다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업환경 요인과 대표 질환&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;요인&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;질환&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;증상&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;국소진동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;레이노 병(백랍병)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손가락이 창백해지고 아프다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전신진동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;요통 · 내장 하수&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;저주파 진동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;소음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C5-dip 현상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4,000 [Hz] 에서 청력이 먼저 떨어진다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분진(유리규산)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;규폐증&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;폐 섬유화&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;망간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;파킨슨 유사 증상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중추신경 장해&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;열사병 · 열경련&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;레이노 병&lt;/strong&gt;이다. &lt;strong&gt;손가락이 하얗게 질린다&lt;/strong&gt;하여 &lt;strong&gt;백랍병(白蠟病)&lt;/strong&gt; 이라고도 한다. 착암기·그라인더 같은 &lt;strong&gt;진동공구&lt;/strong&gt;를 오래 쓰면 생긴다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업환경 요인과 대표 질환&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;요인&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;질환&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;증상&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;국소진동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;레이노 병(백랍병)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손가락이 창백해지고 아프다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전신진동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;요통 · 내장 하수&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;저주파 진동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;소음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;C5-dip 현상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4,000 [Hz]에서 청력이 먼저 떨어진다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분진(유리규산)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;규폐증&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;폐 섬유화&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;망간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;파킨슨 유사 증상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중추신경 장해&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;열사병 · 열경련&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH36" s="32" t="inlineStr">
         <is>
-          <t>② 파킨슨 병은 망간 중독 등에서 보이는 중추신경 장해다.&lt;br&gt;③ 규폐증은 유리규산 분진에 의한 폐질환이다.&lt;br&gt;④ C5-dip 은 소음성 난청에서 4,000 [Hz] 부터 청력이 떨어지는 현상이다.</t>
+          <t>② 파킨슨 병은 망간 중독 등에서 보이는 중추신경 장해다.&lt;br&gt;③ 규폐증은 유리규산 분진에 의한 폐질환이다.&lt;br&gt;④ C5-dip은 소음성 난청에서 4,000 [Hz]부터 청력이 떨어지는 현상이다.</t>
         </is>
       </c>
       <c r="AI36" s="32" t="inlineStr">
@@ -5978,17 +5978,17 @@
       </c>
       <c r="AG38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1,000 [Hz] 에서는 dB 과 phon 이 같다&lt;/strong&gt;. 70 [dB] 이면 &lt;strong&gt;70 [phon]&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;phon 과 sone&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;관계&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;dB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;음압수준&lt;/u&gt; — 물리량&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [Hz] 에서 phon 과 같다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;phon&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감각적 크기 수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,000 [Hz] 순음의 dB 값으로 정의&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sone&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느끼는 크기의 비율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\mathrm{sone} = 2^{( \mathrm{phon} - 40 ) / 10}$ · &lt;u&gt;40 [phon] 이 1 [sone]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;1,000 [Hz] 에서는 dB과 phon이 같다&lt;/strong&gt;. 70 [dB] 이면 &lt;strong&gt;70 [phon]&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;phon과 sone&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;관계&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;dB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;음압수준&lt;/u&gt; — 물리량&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [Hz]에서 phon과 같다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;phon&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;감각적 크기 수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1,000 [Hz] 순음의 dB 값으로 정의&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sone&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느끼는 크기의 비율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\mathrm{sone} = 2^{( \mathrm{phon} - 40 ) / 10}$ · &lt;u&gt;40 [phon]이 1 [sone]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH38" s="32" t="inlineStr">
         <is>
-          <t>① 50 [phon] 은 음압수준이 50 [dB] 일 때다.&lt;br&gt;③ 90 [phon] 은 90 [dB] 일 때다.&lt;br&gt;④ 100 [phon] 은 100 [dB] 일 때다.</t>
+          <t>① 50 [phon]은 음압수준이 50 [dB] 일 때다.&lt;br&gt;③ 90 [phon]은 90 [dB] 일 때다.&lt;br&gt;④ 100 [phon]은 100 [dB] 일 때다.</t>
         </is>
       </c>
       <c r="AI38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;phon 과 sone&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;phon 의 정의 자체가 「1,000 [Hz] 순음의 dB 값」&lt;/strong&gt;이다. 그래서 1,000 [Hz] 에서는 두 값이 언제나 같다. &lt;strong&gt;「몇 배 크게 들린다」는 물음은 sone&lt;/strong&gt;으로 옮겨 풀어야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,000 [Hz] 에서는 dB = phon&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;phon과 sone&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;phon의 정의 자체가 「1,000 [Hz] 순음의 dB 값」&lt;/strong&gt;이다. 그래서 1,000 [Hz] 에서는 두 값이 언제나 같다. &lt;strong&gt;「몇 배 크게 들린다」는 물음은 sone&lt;/strong&gt;으로 옮겨 풀어야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1,000 [Hz] 에서는 dB = phon&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6236,17 +6236,17 @@
       </c>
       <c r="AG40" s="32" t="inlineStr">
         <is>
-          <t>허용시간은 &lt;strong&gt;90 [dB] 8시간, 95 [dB] 4시간, 100 [dB] 2시간&lt;/strong&gt;이다. $\mathrm{TND} = \dfrac{1}{2} + \dfrac{1}{4} + \dfrac{1}{8} = 0.5 + 0.25 + 0.125 = 0.875$ 다. &lt;strong&gt;1 을 넘지 않으므로 적합&lt;/strong&gt; 하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;소음수준별 허용 노출시간&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;소음&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;허용시간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;소음&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;허용시간&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;90 [dB]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;105 [dB]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1시간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;95 [dB]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;110 [dB]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30분&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;100 [dB]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;115 [dB]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15분&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>허용시간은 &lt;strong&gt;90 [dB] 8시간, 95 [dB] 4시간, 100 [dB] 2시간&lt;/strong&gt;이다. $\mathrm{TND} = \dfrac{1}{2} + \dfrac{1}{4} + \dfrac{1}{8} = 0.5 + 0.25 + 0.125 = 0.875$다. &lt;strong&gt;1을 넘지 않으므로 적합&lt;/strong&gt;하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;소음수준별 허용 노출시간&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;소음&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;허용시간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;소음&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;허용시간&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;90 [dB]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;105 [dB]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1시간&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;95 [dB]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;110 [dB]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30분&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;100 [dB]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;115 [dB]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15분&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH40" s="32" t="inlineStr">
         <is>
-          <t>① 0.785 는 계산과 맞지 않는다.&lt;br&gt;③ 0.985 도 맞지 않는다.&lt;br&gt;④ 1.085 도 맞지 않으며, 이 문항은 1 을 넘지 않아 적합하다.</t>
+          <t>① 0.785는 계산과 맞지 않는다.&lt;br&gt;③ 0.985 도 맞지 않는다.&lt;br&gt;④ 1.085 도 맞지 않으며, 이 문항은 1을 넘지 않아 적합하다.</t>
         </is>
       </c>
       <c r="AI40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;총 소음량(TND, Total Noise Dose)&lt;/strong&gt;&lt;br&gt;$\mathrm{TND} = \sum \dfrac{\text{실제 노출시간}}{\text{허용 노출시간}}$ 이다. &lt;strong&gt;1 을 넘으면 부적합&lt;/strong&gt;이다. &lt;strong&gt;5 [dB] 오를 때마다 허용시간이 절반&lt;/strong&gt;이라는 규칙만 알면 표를 외울 필요가 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;몫을 더해 1 과 견준다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;총 소음량(TND, Total Noise Dose)&lt;/strong&gt;&lt;br&gt;$\mathrm{TND} = \sum \dfrac{\text{실제 노출시간}}{\text{허용 노출시간}}$이다. &lt;strong&gt;1을 넘으면 부적합&lt;/strong&gt;이다. &lt;strong&gt;5 [dB] 오를 때마다 허용시간이 절반&lt;/strong&gt;이라는 규칙만 알면 표를 외울 필요가 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;몫을 더해 1과 견준다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7139,12 +7139,12 @@
       </c>
       <c r="AG47" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;12 [mm] 이내&lt;/strong&gt;다. 더 벌어지면 켠 자리가 다시 닫히며 톱날을 물어 &lt;strong&gt;반발&lt;/strong&gt; 한다.</t>
+          <t>&lt;strong&gt;12 [mm] 이내&lt;/strong&gt;다. 더 벌어지면 켠 자리가 다시 닫히며 톱날을 물어 &lt;strong&gt;반발&lt;/strong&gt;한다.</t>
         </is>
       </c>
       <c r="AH47" s="32" t="inlineStr">
         <is>
-          <t>② 14 [mm] 는 기준을 넘는다.&lt;br&gt;③ 16 [mm] 도 넘는다.&lt;br&gt;④ 18 [mm] 도 넘는다.</t>
+          <t>② 14 [mm]는 기준을 넘는다.&lt;br&gt;③ 16 [mm] 도 넘는다.&lt;br&gt;④ 18 [mm] 도 넘는다.</t>
         </is>
       </c>
       <c r="AI47" s="32" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="AH52" s="32" t="inlineStr">
         <is>
-          <t>① 역전방지장치에 「권과방지식」은 없다 — 권과방지는 양중기의 것이다.&lt;br&gt;② 비상정지장치는 반드시 부착해야 한다.&lt;br&gt;④ 롤러컨베이어의 방호판과 롤 사이의 최대간격은 8 [mm] 가 아니라 5 [mm] 다.</t>
+          <t>① 역전방지장치에 「권과방지식」은 없다 — 권과방지는 양중기의 것이다.&lt;br&gt;② 비상정지장치는 반드시 부착해야 한다.&lt;br&gt;④ 롤러컨베이어의 방호판과 롤 사이의 최대간격은 8 [mm]가 아니라 5 [mm]다.</t>
         </is>
       </c>
       <c r="AI52" s="32" t="inlineStr">
@@ -7917,17 +7917,17 @@
       </c>
       <c r="AG53" s="32" t="inlineStr">
         <is>
-          <t>$Y = 6 + 0.15 X$ 를 $X$ 에 대해 푼다. $30 = 6 + 0.15 X$ 이므로 $0.15 X = 24$, $X = 160$ [mm] 다.</t>
+          <t>$Y = 6 + 0.15 X$를 $X$에 대해 푼다. $30 = 6 + 0.15 X$이므로 $0.15 X = 24$, $X = 160$ [mm]다.</t>
         </is>
       </c>
       <c r="AH53" s="32" t="inlineStr">
         <is>
-          <t>① 154 [mm] 는 계산과 맞지 않는다.&lt;br&gt;③ 166 [mm] 도 맞지 않는다.&lt;br&gt;④ 172 [mm] 도 맞지 않는다.</t>
+          <t>① 154 [mm]는 계산과 맞지 않는다.&lt;br&gt;③ 166 [mm] 도 맞지 않는다.&lt;br&gt;④ 172 [mm] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI53" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;ILO 규정 — 가드 개구부의 안전간격&lt;/strong&gt;&lt;br&gt;$Y$ 는 &lt;strong&gt;개구부 간격&lt;/strong&gt;, $X$ 는 &lt;strong&gt;가드와 위험점 사이의 거리&lt;/strong&gt;다. &lt;strong&gt;묻는 것이 어느 쪽인지&lt;/strong&gt;부터 확인해야 한다. $X \ge 160$ 이면 $Y = 30$ 에서 멈추므로, 이 문항은 &lt;strong&gt;경계값&lt;/strong&gt;에 해당한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $Y = 6 + 0.15 X$ — &lt;u&gt;거꾸로 푸는 문항도 나온다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;ILO 규정 — 가드 개구부의 안전간격&lt;/strong&gt;&lt;br&gt;$Y$는 &lt;strong&gt;개구부 간격&lt;/strong&gt;, $X$는 &lt;strong&gt;가드와 위험점 사이의 거리&lt;/strong&gt;다. &lt;strong&gt;묻는 것이 어느 쪽인지&lt;/strong&gt;부터 확인해야 한다. $X \ge 160$이면 $Y = 30$에서 멈추므로, 이 문항은 &lt;strong&gt;경계값&lt;/strong&gt;에 해당한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $Y = 6 + 0.15 X$ — &lt;u&gt;거꾸로 푸는 문항도 나온다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="AI55" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제116조 — 압력방출장치&lt;/strong&gt;&lt;br&gt;작동시험은 &lt;strong&gt;1년에 1회 이상&lt;/strong&gt;이며 &lt;strong&gt;공정안전보고서 이행수준 평가결과가 우수한 사업장은 4년에 1회&lt;/strong&gt;다. 검사 뒤에는 &lt;strong&gt;납으로 봉인&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하나는 최고사용압력 이하, 다른 하나는 1.05배 이하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C116%EC%A1%B0" target="_blank"&gt;제116조(압력방출장치)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ ① 사업주는 보일러의 안전한 가동을 위하여 보일러 규격에 맞는 압력방출장치를 1개 또는 2개 이상 설치하고 최고사용압력(설계압력 또는 최고허용압력을 말한다. 이하 같다) 이하에서 작동되도록 하여야 한다. 다만, 압력방출장치가 2개 이상 설치된 경우에는 최고사용압력 이하에서 1개가 작동되고, 다른 압력방출장치는 최고사용압력 &lt;strong&gt;1.05배 이하&lt;/strong&gt;에서 작동되도록 부착하여야 한다.&lt;br&gt;▶ ② 제1항의 압력방출장치는 매년 1회 이상 「국가표준기본법」 제14조제3항에 따라 산업통상부장관의 지정을 받은 국가교정업무 전담기관(이하 "국가교정기관"이라 한다)에서 교정을 받은 압력계를 이용하여 설정압력에서 압력방출장치가 적정하게 작동하는지를 검사한 후 &lt;strong&gt;납으로 봉인&lt;/strong&gt;하여 사용하여야 한다. 다만, 영 제43조에 따른 공정안전보고서 제출 대상으로서 고용노동부장관이 실시하는 공정안전보고서 이행상태 &lt;strong&gt;평가결과가 우수한 사업장은&lt;/strong&gt; 압력방출장치에 대하여 4년마다 1회 이상 설정압력에서 압력방출장치가 적정하게 작동하는지를 검사할 수 있다. &amp;lt;개정 2013.3.23, 2019.12.26, 2025.10.1&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제116조 — 압력방출장치&lt;/strong&gt;&lt;br&gt;작동시험은 &lt;strong&gt;1년에 1회 이상&lt;/strong&gt;이며 &lt;strong&gt;공정안전보고서 이행수준 평가결과가 우수한 사업장은 4년에 1회&lt;/strong&gt;다. 검사 뒤에는 &lt;strong&gt;납으로 봉인&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하나는 최고사용압력 이하, 다른 하나는 1.05배 이하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C116%EC%A1%B0" target="_blank"&gt;제116조(압력방출장치)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ ① 사업주는 보일러의 안전한 가동을 위하여 보일러 규격에 맞는 압력방출장치를 1개 또는 2개 이상 설치하고 최고사용압력(설계압력 또는 최고허용압력을 말한다. 이하 같다) 이하에서 작동되도록 하여야 한다. 다만, 압력방출장치가 2개 이상 설치된 경우에는 최고사용압력 이하에서 1개가 작동되고, 다른 압력방출장치는 최고사용압력 &lt;strong&gt;1.05배 이하&lt;/strong&gt;에서 작동되도록 부착하여야 한다.&lt;br&gt;▶ ② 제1항의 압력방출장치는 매년 1회 이상 「국가표준기본법」 제14조제3항에 따라 산업통상부장관의 지정을 받은 국가교정업무 전담기관(이하 "국가교정기관"이라 한다)에서 교정을 받은 압력계를 이용하여 설정압력에서 압력방출장치가 적정하게 작동하는지를 검사한 후 &lt;strong&gt;납으로 봉인&lt;/strong&gt;하여 사용하여야 한다. 다만, 영 제43조에 따른 공정안전보고서 제출 대상으로서 고용노동부장관이 실시하는 공정안전보고서 이행상태 &lt;strong&gt;평가결과가 우수한 사업장은&lt;/strong&gt; 압력방출장치에 대하여 4년마다 1회 이상 설정압력에서 압력방출장치가 적정하게 작동하는지를 검사할 수 있다. &amp;lt;개정 2013.3.23, 2019.12.26, 2025.10.1&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="AG57" s="32" t="inlineStr">
         <is>
-          <t>가스집합장치는 &lt;strong&gt;화기를 사용하는 설비로부터 5 [m] 이상&lt;/strong&gt; 떨어뜨린다. 3 [m] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;용접장치의 거리 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가스집합장치 ↔ 화기를 사용하는 설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세틸렌 발생기 ↔ 화기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m] 이내 금연·화기 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발생기실 ↔ 화기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [m] 이내 금연·화기 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발생기실 ↔ 건물의 벽&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>가스집합장치는 &lt;strong&gt;화기를 사용하는 설비로부터 5 [m] 이상&lt;/strong&gt; 떨어뜨린다. 3 [m]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;용접장치의 거리 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가스집합장치 ↔ 화기를 사용하는 설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아세틸렌 발생기 ↔ 화기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [m] 이내 금연·화기 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발생기실 ↔ 화기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [m] 이내 금연·화기 금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발생기실 ↔ 건물의 벽&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH57" s="32" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>안정도는 $\dfrac{\text{수직높이}}{\text{수평거리}} \times 100 = \dfrac{1.5}{12} \times 100 = 12.5$ [%] 다. &lt;strong&gt;주행 시 전후 안정도 기준은 18 [%] 이내&lt;/strong&gt;이므로 &lt;strong&gt;만족&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안정도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 — 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5톤 이상은 &lt;u&gt;3.5 [%]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 — 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 — 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 — 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(15 + 1.1V) [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;V 는 [km/h]&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_02_057_exp1.png"&gt;&lt;em&gt;지게차 안정도 — 하역은 작고 주행은 크다&lt;/em&gt;</t>
+          <t>안정도는 $\dfrac{\text{수직높이}}{\text{수평거리}} \times 100 = \dfrac{1.5}{12} \times 100 = 12.5$ [%]다. &lt;strong&gt;주행 시 전후 안정도 기준은 18 [%] 이내&lt;/strong&gt;이므로 &lt;strong&gt;만족&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안정도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 — 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5톤 이상은 &lt;u&gt;3.5 [%]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 — 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 — 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18 [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 — 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(15 + 1.1V) [%] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;V는 [km/h]&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;&lt;img src="safe_A_2025_02_057_exp1.png"&gt;&lt;em&gt;지게차 안정도 — 하역은 작고 주행은 크다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
-          <t>① 12.5 [%] 는 18 [%] 이내이므로 기준을 만족한다.&lt;br&gt;③ 안정도 값이 25 [%] 가 아니다.&lt;br&gt;④ 값과 판정이 둘 다 어긋난다.</t>
+          <t>① 12.5 [%]는 18 [%] 이내이므로 기준을 만족한다.&lt;br&gt;③ 안정도 값이 25 [%]가 아니다.&lt;br&gt;④ 값과 판정이 둘 다 어긋난다.</t>
         </is>
       </c>
       <c r="AI59" s="32" t="inlineStr">
@@ -8820,17 +8820,17 @@
       </c>
       <c r="AG60" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;6 은 스트랜드(꼬임) 수&lt;/strong&gt;, &lt;strong&gt;19 는 스트랜드 하나에 든 소선 수&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프 호칭 「6 × 19」&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;자리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앞의 6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;스트랜드(strand) 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;심강 둘레에 꼬인 다발의 개수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뒤의 19&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;스트랜드 하나에 든 소선 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전체 소선은 6 × 19 = 114 가닥&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;6은 스트랜드(꼬임) 수&lt;/strong&gt;, &lt;strong&gt;19는 스트랜드 하나에 든 소선 수&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프 호칭 「6 × 19」&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;자리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앞의 6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;스트랜드(strand) 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;심강 둘레에 꼬인 다발의 개수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뒤의 19&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;스트랜드 하나에 든 소선 수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전체 소선은 6 × 19 = 114 가닥&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH60" s="32" t="inlineStr">
         <is>
-          <t>① 소선의 지름은 호칭에 들어가지 않는다.&lt;br&gt;② 소선의 수량은 뒤의 19 다.&lt;br&gt;④ 최대인장강도는 호칭이 아니라 따로 표기한다.</t>
+          <t>① 소선의 지름은 호칭에 들어가지 않는다.&lt;br&gt;② 소선의 수량은 뒤의 19다.&lt;br&gt;④ 최대인장강도는 호칭이 아니라 따로 표기한다.</t>
         </is>
       </c>
       <c r="AI60" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;와이어로프의 호칭&lt;/strong&gt;&lt;br&gt;와이어로프의 폐기 기준도 함께 나온다 — &lt;strong&gt;소선이 10 [%] 이상 끊어진 것 · 지름 감소가 공칭지름의 7 [%] 를 초과한 것 · 꼬인 것 · 심하게 변형되거나 부식된 것 · 열이나 전기불꽃에 손상된 것&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;앞은 다발, 뒤는 가닥&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;와이어로프의 호칭&lt;/strong&gt;&lt;br&gt;와이어로프의 폐기 기준도 함께 나온다 — &lt;strong&gt;소선이 10 [%] 이상 끊어진 것 · 지름 감소가 공칭지름의 7 [%]를 초과한 것 · 꼬인 것 · 심하게 변형되거나 부식된 것 · 열이나 전기불꽃에 손상된 것&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;앞은 다발, 뒤는 가닥&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8958,12 +8958,12 @@
       </c>
       <c r="AH61" s="32" t="inlineStr">
         <is>
-          <t>② 가가 60 [cm] 면 난간이 너무 낮다.&lt;br&gt;③ 나가 20 [cm] 라는 기준은 없다.&lt;br&gt;④ 가·나 둘 다 어긋난다.</t>
+          <t>② 가가 60 [cm] 면 난간이 너무 낮다.&lt;br&gt;③ 나가 20 [cm]라는 기준은 없다.&lt;br&gt;④ 가·나 둘 다 어긋난다.</t>
         </is>
       </c>
       <c r="AI61" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제13조 — 안전난간의 구조 및 설치요건&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;상부 난간대 90 [cm] 이상&lt;/strong&gt;이며 &lt;strong&gt;상한은 없다&lt;/strong&gt;. 120 [cm] 는 &lt;strong&gt;중간 난간대를 몇 개 둘 것인가&lt;/strong&gt;를 가르는 분기점일 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;난간 90, 폭목 10, 지름 2.7, 하중 100&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C13%EC%A1%B0" target="_blank"&gt;제13조(안전난간의 구조 및 설치요건)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 근로자의 추락 등의 위험을 방지하기 위하여 안전난간을 설치하는 경우 다음 각 호의 기준에 맞는 구조로 설치해야 한다. &amp;lt;개정 2015.12.31, 2023.11.14&amp;gt;&lt;br&gt; 1. 상부 난간대, 중간 난간대, 발끝막이판 및 난간기둥으로 구성할 것. 다만, 중간 난간대, 발끝막이판 및 난간기둥은 이와 비슷한 구조와 성능을 가진 것으로 대체할 수 있다.&lt;br&gt;▶  2. 상부 난간대는 바닥면ㆍ발판 또는 경사로의 표면(이하 "바닥면등"이라 한다)으로부터 &lt;strong&gt;90센티미터&lt;/strong&gt; 이상 지점에 설치하고, 상부 난간대를 120센티미터 이하에 설치하는 경우에는 중간 난간대는 상부 난간대와 바닥면등의 중간에 설치해야 하며, 120센티미터 이상 지점에 설치하는 경우에는 &lt;strong&gt;중간 난간대를&lt;/strong&gt; 2단 이상으로 균등하게 설치하고 난간의 상하 간격은 60센티미터 이하가 되도록 할 것. 다만, 난간기둥 간의 간격이 25센티미터 이하인 경우에는 &lt;strong&gt;중간 난간대를&lt;/strong&gt; 설치하지 않을 수 있다.&lt;br&gt;▶  3. 발끝막이판은 바닥면등으로부터 &lt;strong&gt;10센티미터&lt;/strong&gt; 이상의 높이를 유지할 것. 다만, 물체가 떨어지거나 날아올 위험이 없거나 그 위험을 방지할 수 있는 망을 설치하는 등 필요한 예방 조치를 한 장소는 제외한다.&lt;br&gt;▶  4. 난간기둥은 상부 난간대와 &lt;strong&gt;중간 난간대를&lt;/strong&gt; 견고하게 떠받칠 수 있도록 적정한 간격을 유지할 것&lt;br&gt; 5. 상부 난간대와 중간 난간대는 난간 길이 전체에 걸쳐 바닥면등과 평행을 유지할 것&lt;br&gt; 6. 난간대는 지름 2.7센티미터 이상의 금속제 파이프나 그 이상의 강도가 있는 재료일 것&lt;br&gt; 7. 안전난간은 구조적으로 가장 취약한 지점에서 가장 취약한 방향으로 작용하는 100킬로그램 이상의 하중에 견딜 수 있는 튼튼한 구조일 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제13조 — 안전난간의 구조 및 설치요건&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;상부 난간대 90 [cm] 이상&lt;/strong&gt;이며 &lt;strong&gt;상한은 없다&lt;/strong&gt;. 120 [cm]는 &lt;strong&gt;중간 난간대를 몇 개 둘 것인가&lt;/strong&gt;를 가르는 분기점일 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;난간 90, 폭목 10, 지름 2.7, 하중 100&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C13%EC%A1%B0" target="_blank"&gt;제13조(안전난간의 구조 및 설치요건)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 근로자의 추락 등의 위험을 방지하기 위하여 안전난간을 설치하는 경우 다음 각 호의 기준에 맞는 구조로 설치해야 한다. &amp;lt;개정 2015.12.31, 2023.11.14&amp;gt;&lt;br&gt; 1. 상부 난간대, 중간 난간대, 발끝막이판 및 난간기둥으로 구성할 것. 다만, 중간 난간대, 발끝막이판 및 난간기둥은 이와 비슷한 구조와 성능을 가진 것으로 대체할 수 있다.&lt;br&gt;▶  2. 상부 난간대는 바닥면ㆍ발판 또는 경사로의 표면(이하 "바닥면등"이라 한다)으로부터 &lt;strong&gt;90센티미터&lt;/strong&gt; 이상 지점에 설치하고, 상부 난간대를 120센티미터 이하에 설치하는 경우에는 중간 난간대는 상부 난간대와 바닥면등의 중간에 설치해야 하며, 120센티미터 이상 지점에 설치하는 경우에는 &lt;strong&gt;중간 난간대를&lt;/strong&gt; 2단 이상으로 균등하게 설치하고 난간의 상하 간격은 60센티미터 이하가 되도록 할 것. 다만, 난간기둥 간의 간격이 25센티미터 이하인 경우에는 &lt;strong&gt;중간 난간대를&lt;/strong&gt; 설치하지 않을 수 있다.&lt;br&gt;▶  3. 발끝막이판은 바닥면등으로부터 &lt;strong&gt;10센티미터&lt;/strong&gt; 이상의 높이를 유지할 것. 다만, 물체가 떨어지거나 날아올 위험이 없거나 그 위험을 방지할 수 있는 망을 설치하는 등 필요한 예방 조치를 한 장소는 제외한다.&lt;br&gt;▶  4. 난간기둥은 상부 난간대와 &lt;strong&gt;중간 난간대를&lt;/strong&gt; 견고하게 떠받칠 수 있도록 적정한 간격을 유지할 것&lt;br&gt; 5. 상부 난간대와 중간 난간대는 난간 길이 전체에 걸쳐 바닥면등과 평행을 유지할 것&lt;br&gt; 6. 난간대는 지름 2.7센티미터 이상의 금속제 파이프나 그 이상의 강도가 있는 재료일 것&lt;br&gt; 7. 안전난간은 구조적으로 가장 취약한 지점에서 가장 취약한 방향으로 작용하는 100킬로그램 이상의 하중에 견딜 수 있는 튼튼한 구조일 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -9216,12 +9216,12 @@
       </c>
       <c r="AH63" s="32" t="inlineStr">
         <is>
-          <t>① 동작시간 0.1초는 너무 느리다.&lt;br&gt;③ 50 [mA] 는 심실세동 위험 영역에 든다.&lt;br&gt;④ 50 [mA]·0.3초는 둘 다 어긋난다.</t>
+          <t>① 동작시간 0.1초는 너무 느리다.&lt;br&gt;③ 50 [mA]는 심실세동 위험 영역에 든다.&lt;br&gt;④ 50 [mA]·0.3초는 둘 다 어긋난다.</t>
         </is>
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;한국전기설비규정(KEC) 211.2.4 — 누전차단기의 시설&lt;/strong&gt;&lt;br&gt;30 [mA]·0.03초는 &lt;strong&gt;Dalziel 의 심실세동 한계 &lt;/strong&gt;$I = 165 / \sqrt{T}$에서 나온 값에 큰 여유를 둔 것이다. &lt;strong&gt;전압이나 인체저항이 얼마든 규격은 같다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;일반 30, 물기 15 — 시간은 둘 다 0.03초&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;한국전기설비규정(KEC) 211.2.4 — 누전차단기의 시설&lt;/strong&gt;&lt;br&gt;30 [mA]·0.03초는 &lt;strong&gt;Dalziel의 심실세동 한계 &lt;/strong&gt;$I = 165 / \sqrt{T}$에서 나온 값에 큰 여유를 둔 것이다. &lt;strong&gt;전압이나 인체저항이 얼마든 규격은 같다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;일반 30, 물기 15 — 시간은 둘 다 0.03초&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="AI72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;폭발위험장소의 구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;가스는 0·1·2종, 분진은 20·21·22종&lt;/strong&gt;으로 앞에 20 을 붙인다. 뜻은 완전히 나란하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;분진은 20 · 21 · 22 셋&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;폭발위험장소의 구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;가스는 0·1·2종, 분진은 20·21·22종&lt;/strong&gt;으로 앞에 20을 붙인다. 뜻은 완전히 나란하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;분진은 20 · 21 · 22 셋&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="AH75" s="32" t="inlineStr">
         <is>
-          <t>① 0.3 [m] 는 크레인 통로 간격의 기준이다.&lt;br&gt;② 0.5 [m] 라는 기준은 없다.&lt;br&gt;④ 1.5 [m] 는 발생기실과 건물 벽의 거리다.</t>
+          <t>① 0.3 [m]는 크레인 통로 간격의 기준이다.&lt;br&gt;② 0.5 [m]라는 기준은 없다.&lt;br&gt;④ 1.5 [m]는 발생기실과 건물 벽의 거리다.</t>
         </is>
       </c>
       <c r="AI75" s="32" t="inlineStr">
@@ -10880,17 +10880,17 @@
       </c>
       <c r="AG76" s="32" t="inlineStr">
         <is>
-          <t>저압 측 최대공급전류는 $15 {,} 000 / 100 = 150$ [A] 다. 누설전류는 &lt;strong&gt;최대공급전류의 1/2,000 이하&lt;/strong&gt;이므로 $150 / 2 {,} 000 = 0.075$ [A] 다.</t>
+          <t>저압 측 최대공급전류는 $15 {,} 000 / 100 = 150$ [A]다. 누설전류는 &lt;strong&gt;최대공급전류의 1/2,000 이하&lt;/strong&gt;이므로 $150 / 2 {,} 000 = 0.075$ [A]다.</t>
         </is>
       </c>
       <c r="AH76" s="32" t="inlineStr">
         <is>
-          <t>① 0.025 [A] 는 계산과 맞지 않는다.&lt;br&gt;② 0.045 [A] 도 맞지 않는다.&lt;br&gt;④ 0.085 [A] 도 맞지 않는다.</t>
+          <t>① 0.025 [A]는 계산과 맞지 않는다.&lt;br&gt;② 0.045 [A] 도 맞지 않는다.&lt;br&gt;④ 0.085 [A] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI76" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;저압 전선로의 누설전류 한도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;저압 측 전압(100 [V])으로 나눈다&lt;/strong&gt;는 점이 갈림길이다. 6,600 [V] 로 나누면 고압 측 전류가 나와 답이 크게 어긋난다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;용량 ÷ 저압 전압 ÷ 2,000&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;저압 전선로의 누설전류 한도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;저압 측 전압(100 [V])으로 나눈다&lt;/strong&gt;는 점이 갈림길이다. 6,600 [V]로 나누면 고압 측 전류가 나와 답이 크게 어긋난다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;용량 ÷ 저압 전압 ÷ 2,000&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="AH77" s="32" t="inlineStr">
         <is>
-          <t>① 10 ~ 20 [A/mm²] 는 정상 사용 범위에 가깝다.&lt;br&gt;② 30 ~ 50 [A/mm²] 는 인화·착화 단계다.&lt;br&gt;④ 130 ~ 200 [A/mm²] 는 순간용단 단계다.</t>
+          <t>① 10 ~ 20 [A/mm²]는 정상 사용 범위에 가깝다.&lt;br&gt;② 30 ~ 50 [A/mm²]는 인화·착화 단계다.&lt;br&gt;④ 130 ~ 200 [A/mm²]는 순간용단 단계다.</t>
         </is>
       </c>
       <c r="AI77" s="32" t="inlineStr">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="AG80" s="32" t="inlineStr">
         <is>
-          <t>제2종 접지선은 &lt;strong&gt;공칭단면적 16 [㎟] 이상&lt;/strong&gt;이다. 2.5 [㎟] 가 아니다. 다만 &lt;strong&gt;이 종별 구분 자체가 지금은 폐지되었다&lt;/strong&gt;. 아래 주의사항을 함께 보아야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;옛 접지공사의 종별 (지금은 폐지)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종별&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접지저항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접지선 굵기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;적용&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제1종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [㎟] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고압·특고압 기기 외함&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제2종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;150 / 1선지락전류 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;16 [㎟] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;변압기 중성점&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제3종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 [㎟] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;400 [V] 미만 저압 기기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;특별 제3종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 [㎟] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;400 [V] 이상 저압 기기&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>제2종 접지선은 &lt;strong&gt;공칭단면적 16 [㎟] 이상&lt;/strong&gt;이다. 2.5 [㎟]가 아니다. 다만 &lt;strong&gt;이 종별 구분 자체가 지금은 폐지되었다&lt;/strong&gt;. 아래 주의사항을 함께 보아야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;옛 접지공사의 종별 (지금은 폐지)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종별&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접지저항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접지선 굵기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;적용&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제1종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 [㎟] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고압·특고압 기기 외함&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제2종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;150 / 1선지락전류 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;16 [㎟] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;변압기 중성점&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제3종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 [㎟] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;400 [V] 미만 저압 기기&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;특별 제3종&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [Ω] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.5 [㎟] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;400 [V] 이상 저압 기기&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH80" s="32" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="AG84" s="32" t="inlineStr">
         <is>
-          <t>용기 하나에 담을 수 있는 양은 $W = \dfrac{V}{C} = \dfrac{50}{2.35} \fallingdotseq 21.28$ [kg] 이다. $310 / 21.28 \fallingdotseq 14.6$ 이므로 &lt;strong&gt;15개&lt;/strong&gt;가 필요하다.</t>
+          <t>용기 하나에 담을 수 있는 양은 $W = \dfrac{V}{C} = \dfrac{50}{2.35} \fallingdotseq 21.28$ [kg]이다. $310 / 21.28 \fallingdotseq 14.6$이므로 &lt;strong&gt;15개&lt;/strong&gt;가 필요하다.</t>
         </is>
       </c>
       <c r="AH84" s="32" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="AI84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;액화가스의 충전량&lt;/strong&gt;&lt;br&gt;$W = V / C$ 다. $V$ 는 내용적 [L], $C$ 는 가스정수다. &lt;strong&gt;나눈 값이 딱 떨어지지 않으면 올림&lt;/strong&gt; 한다 — 14.6개를 쓸 수는 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $W = V \div C$ — &lt;u&gt;개수는 올림&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;액화가스의 충전량&lt;/strong&gt;&lt;br&gt;$W = V / C$다. $V$는 내용적 [L], $C$는 가스정수다. &lt;strong&gt;나눈 값이 딱 떨어지지 않으면 올림&lt;/strong&gt;한다 — 14.6개를 쓸 수는 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $W = V \div C$ — &lt;u&gt;개수는 올림&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12170,17 +12170,17 @@
       </c>
       <c r="AG86" s="32" t="inlineStr">
         <is>
-          <t>$C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 ( n + \dfrac{m}{4} - \dfrac{l}{2} )}$ 다. 메탄은 $n = 1 , m = 4$ 이므로 $n + m / 4 = 2$ 다. $C_{\mathrm{st}} = 100 / ( 1 + 4.773 \times 2 ) = 100 / 10.546 \fallingdotseq 9.48 \fallingdotseq 9.50$ [vol%] 다.</t>
+          <t>$C_{\mathrm{st}} = \dfrac{100}{1 + 4.773 ( n + \dfrac{m}{4} - \dfrac{l}{2} )}$다. 메탄은 $n = 1 , m = 4$이므로 $n + m / 4 = 2$다. $C_{\mathrm{st}} = 100 / ( 1 + 4.773 \times 2 ) = 100 / 10.546 \fallingdotseq 9.48 \fallingdotseq 9.50$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH86" s="32" t="inlineStr">
         <is>
-          <t>① 2.21 [vol%] 는 프로판 쪽 값에 가깝다.&lt;br&gt;② 4.03 [vol%] 도 맞지 않는다.&lt;br&gt;③ 5.76 [vol%] 도 맞지 않는다.</t>
+          <t>① 2.21 [vol%]는 프로판 쪽 값에 가깝다.&lt;br&gt;② 4.03 [vol%] 도 맞지 않는다.&lt;br&gt;③ 5.76 [vol%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI86" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;화학양론조성($C_{\mathrm{st}}$)&lt;/strong&gt;&lt;br&gt;4.773 은 &lt;strong&gt;공기 중 산소가 21 [%] 이므로 &lt;/strong&gt;$1 / 0.21$에서 나온 값이다. &lt;strong&gt;최소산소농도(MOC)&lt;/strong&gt;나 &lt;strong&gt;폭발하한계 어림값(&lt;/strong&gt;$0.55 C_{\mathrm{st}}$&lt;strong&gt;)&lt;/strong&gt;을 구할 때도 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $C_{\mathrm{st}} = 100 \div ( 1 + 4.773 \times ( n + m / 4 ) )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;화학양론조성($C_{\mathrm{st}}$)&lt;/strong&gt;&lt;br&gt;4.773은 &lt;strong&gt;공기 중 산소가 21 [%]이므로 &lt;/strong&gt;$1 / 0.21$에서 나온 값이다. &lt;strong&gt;최소산소농도(MOC)&lt;/strong&gt;나 &lt;strong&gt;폭발하한계 어림값(&lt;/strong&gt;$0.55 C_{\mathrm{st}}$&lt;strong&gt;)&lt;/strong&gt;을 구할 때도 쓴다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $C_{\mathrm{st}} = 100 \div ( 1 + 4.773 \times ( n + m / 4 ) )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12265,7 +12265,7 @@
       </c>
       <c r="U87" s="32" t="inlineStr">
         <is>
-          <t>공기 중에서 A 가스의 폭발하한계는 2.2vol%이다. 이 폭발하한계 값을 기준으로 하여 표준 상태에서 A 가스와 공기의 혼합기체 1m3 에 함유되어 있는 A 가스의 질량을 구하면 약 몇 g 인가? (단, A가스의 분자량은 26 이다.)</t>
+          <t>공기 중에서 A 가스의 폭발하한계는 2.2vol%이다. 이 폭발하한계 값을 기준으로 하여 표준 상태에서 A 가스와 공기의 혼합기체 1m3에 함유되어 있는 A 가스의 질량을 구하면 약 몇 g 인가? (단, A가스의 분자량은 26이다.)</t>
         </is>
       </c>
       <c r="V87" s="32" t="inlineStr"/>
@@ -12299,17 +12299,17 @@
       </c>
       <c r="AG87" s="32" t="inlineStr">
         <is>
-          <t>혼합기체 1 [m³] 가운데 A 가스는 $1 \times 0.022 = 0.022$ [m³] = 22 [L] 다. 표준상태에서 1몰은 22.4 [L] 이므로 $22 / 22.4 = 0.982$ 몰이다. 질량은 $0.982 \times 26 \fallingdotseq 25.54$ [g] 다.</t>
+          <t>혼합기체 1 [m³] 가운데 A 가스는 $1 \times 0.022 = 0.022$ [m³] = 22 [L]다. 표준상태에서 1몰은 22.4 [L]이므로 $22 / 22.4 = 0.982$ 몰이다. 질량은 $0.982 \times 26 \fallingdotseq 25.54$ [g]다.</t>
         </is>
       </c>
       <c r="AH87" s="32" t="inlineStr">
         <is>
-          <t>① 19.02 [g] 는 계산과 맞지 않는다.&lt;br&gt;③ 29.02 [g] 도 맞지 않는다.&lt;br&gt;④ 35.54 [g] 도 맞지 않는다.</t>
+          <t>① 19.02 [g]는 계산과 맞지 않는다.&lt;br&gt;③ 29.02 [g] 도 맞지 않는다.&lt;br&gt;④ 35.54 [g] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI87" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;표준상태에서 기체의 질량&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;표준상태(0 [℃], 1 [atm])에서 기체 1몰은 22.4 [L]&lt;/strong&gt;다. &lt;strong&gt;부피 → 몰수 → 질량&lt;/strong&gt; 순서로 옮겨 간다. 분자량 26 은 &lt;strong&gt;아세틸렌(C₂H₂)&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;22.4 [L] 가 1몰&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;표준상태에서 기체의 질량&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;표준상태(0 [℃], 1 [atm])에서 기체 1몰은 22.4 [L]&lt;/strong&gt;다. &lt;strong&gt;부피 → 몰수 → 질량&lt;/strong&gt; 순서로 옮겨 간다. 분자량 26은 &lt;strong&gt;아세틸렌(C₂H₂)&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;22.4 [L]가 1몰&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12561,17 +12561,17 @@
       </c>
       <c r="AG89" s="32" t="inlineStr">
         <is>
-          <t>하한은 $\dfrac{100}{L} = \dfrac{70}{5.0} + \dfrac{21}{2.1} + \dfrac{9}{1.8} = 29$ 이므로 $L \fallingdotseq 3.45$ 다. 상한은 $\dfrac{100}{U} = \dfrac{70}{15.0} + \dfrac{21}{9.5} + \dfrac{9}{8.4} = 7.949$ 이므로 $U \fallingdotseq 12.58$ 다.</t>
+          <t>하한은 $\dfrac{100}{L} = \dfrac{70}{5.0} + \dfrac{21}{2.1} + \dfrac{9}{1.8} = 29$이므로 $L \fallingdotseq 3.45$다. 상한은 $\dfrac{100}{U} = \dfrac{70}{15.0} + \dfrac{21}{9.5} + \dfrac{9}{8.4} = 7.949$이므로 $U \fallingdotseq 12.58$다.</t>
         </is>
       </c>
       <c r="AH89" s="32" t="inlineStr">
         <is>
-          <t>① 상한 9.11 은 계산과 맞지 않는다.&lt;br&gt;③ 하한 3.85 도 맞지 않는다.&lt;br&gt;④ 하한과 상한이 둘 다 어긋난다.</t>
+          <t>① 상한 9.11은 계산과 맞지 않는다.&lt;br&gt;③ 하한 3.85 도 맞지 않는다.&lt;br&gt;④ 하한과 상한이 둘 다 어긋난다.</t>
         </is>
       </c>
       <c r="AI89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;르 샤틀리에의 혼합가스 폭발범위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하한과 상한을 따로 계산&lt;/strong&gt; 한다. 식은 같고 대입하는 값만 다르다. 하한 계산이 맞으면 보기 둘이 걸러지므로 &lt;strong&gt;하한부터 구하는 것&lt;/strong&gt;이 빠르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하한 따로, 상한 따로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;르 샤틀리에의 혼합가스 폭발범위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하한과 상한을 따로 계산&lt;/strong&gt;한다. 식은 같고 대입하는 값만 다르다. 하한 계산이 맞으면 보기 둘이 걸러지므로 &lt;strong&gt;하한부터 구하는 것&lt;/strong&gt;이 빠르다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하한 따로, 상한 따로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12819,7 +12819,7 @@
       </c>
       <c r="AG91" s="32" t="inlineStr">
         <is>
-          <t>건축물의 보는 &lt;strong&gt;지상 1층까지&lt;/strong&gt;다. 지상 2층이 아니다. &lt;strong&gt;기둥과 보 모두 지상 1층(6 [m]) 까지&lt;/strong&gt;로 같다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;내화구조로 해야 하는 부분 (규칙 제270조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;부분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;범위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건축물의 기둥 및 보&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지상 1층까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1층 높이가 6 [m] 를 넘으면 6 [m] 까지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물 저장·취급용기의 지지대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지상으로부터 지지대의 끝부분까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 30 [cm] 이하는 제외&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배관·전선관 등의 지지대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지상으로부터 1단까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1단 높이가 6 [m] 를 넘으면 6 [m] 까지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>건축물의 보는 &lt;strong&gt;지상 1층까지&lt;/strong&gt;다. 지상 2층이 아니다. &lt;strong&gt;기둥과 보 모두 지상 1층(6 [m])까지&lt;/strong&gt;로 같다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;내화구조로 해야 하는 부분 (규칙 제270조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;부분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;범위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건축물의 기둥 및 보&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지상 1층까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1층 높이가 6 [m]를 넘으면 6 [m]까지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물 저장·취급용기의 지지대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지상으로부터 지지대의 끝부분까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 30 [cm] 이하는 제외&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배관·전선관 등의 지지대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지상으로부터 1단까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1단 높이가 6 [m]를 넘으면 6 [m]까지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH91" s="32" t="inlineStr">
@@ -13077,12 +13077,12 @@
       </c>
       <c r="AG93" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;수소(H₂)&lt;/strong&gt;가 약 0.019 [mJ] 로 가장 작다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 물질의 최소발화에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;MIE&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이황화탄소 CS₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.009 [mJ]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 작다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소 H₂ · 아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.019 [mJ]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ⅡC 그룹&lt;/u&gt; — 이 문항의 답&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.07 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;ⅡB 그룹&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프로판 C₃H₈&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.25 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;메탄 CH₄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.28 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;벤젠 C₆H₆&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.20 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;수소(H₂)&lt;/strong&gt;가 약 0.019 [mJ]로 가장 작다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;주요 물질의 최소발화에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;MIE&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이황화탄소 CS₂&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.009 [mJ]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가장 작다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소 H₂ · 아세틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.019 [mJ]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ⅡC 그룹&lt;/u&gt; — 이 문항의 답&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;에틸렌&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.07 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;ⅡB 그룹&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프로판 C₃H₈&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.25 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;메탄 CH₄&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.28 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;벤젠 C₆H₆&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.20 [mJ]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH93" s="32" t="inlineStr">
         <is>
-          <t>① 메탄은 약 0.28 [mJ] 다.&lt;br&gt;② 프로판은 약 0.25 [mJ] 다.&lt;br&gt;③ 벤젠은 약 0.20 [mJ] 다.</t>
+          <t>① 메탄은 약 0.28 [mJ]다.&lt;br&gt;② 프로판은 약 0.25 [mJ]다.&lt;br&gt;③ 벤젠은 약 0.20 [mJ]다.</t>
         </is>
       </c>
       <c r="AI93" s="32" t="inlineStr">
@@ -13206,7 +13206,7 @@
       </c>
       <c r="AG94" s="32" t="inlineStr">
         <is>
-          <t>일산화탄소는 &lt;strong&gt;가연성 가스&lt;/strong&gt;다. 폭발범위가 &lt;strong&gt;12.5 ~ 74 [vol%]&lt;/strong&gt;로 넓다. 허용농도도 &lt;strong&gt;30 [ppm]&lt;/strong&gt;이지 10 [ppm] 이 아니다.</t>
+          <t>일산화탄소는 &lt;strong&gt;가연성 가스&lt;/strong&gt;다. 폭발범위가 &lt;strong&gt;12.5 ~ 74 [vol%]&lt;/strong&gt;로 넓다. 허용농도도 &lt;strong&gt;30 [ppm]&lt;/strong&gt;이지 10 [ppm]이 아니다.</t>
         </is>
       </c>
       <c r="AH94" s="32" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="AH101" s="32" t="inlineStr">
         <is>
-          <t>① 1.0 [vol%] 는 벤젠의 하한보다 낮다.&lt;br&gt;③ 2.0 [vol%] 는 하한보다 높다.&lt;br&gt;④ 2.5 [vol%] 는 아세틸렌의 하한이다.</t>
+          <t>① 1.0 [vol%]는 벤젠의 하한보다 낮다.&lt;br&gt;③ 2.0 [vol%]는 하한보다 높다.&lt;br&gt;④ 2.5 [vol%]는 아세틸렌의 하한이다.</t>
         </is>
       </c>
       <c r="AI101" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;주요 가스의 폭발범위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;벤젠과 가솔린은 하한이 1.4 [vol%] 로 거의 같다&lt;/strong&gt;. 둘 다 &lt;strong&gt;인화점이 영하&lt;/strong&gt;라 상온에서 늘 증기가 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;벤젠 1.4 ~ 7.1&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;주요 가스의 폭발범위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;벤젠과 가솔린은 하한이 1.4 [vol%]로 거의 같다&lt;/strong&gt;. 둘 다 &lt;strong&gt;인화점이 영하&lt;/strong&gt;라 상온에서 늘 증기가 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;벤젠 1.4 ~ 7.1&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14238,17 +14238,17 @@
       </c>
       <c r="AG102" s="32" t="inlineStr">
         <is>
-          <t>$\dfrac{100}{L} = \dfrac{50}{5.0} + \dfrac{30}{3.0} + \dfrac{20}{2.1} = 10 + 10 + 9.524 = 29.524$ 이므로 $L = 100 / 29.524 \fallingdotseq 3.4$ [vol%] 다.</t>
+          <t>$\dfrac{100}{L} = \dfrac{50}{5.0} + \dfrac{30}{3.0} + \dfrac{20}{2.1} = 10 + 10 + 9.524 = 29.524$이므로 $L = 100 / 29.524 \fallingdotseq 3.4$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH102" s="32" t="inlineStr">
         <is>
-          <t>① 1.6 [vol%] 는 계산과 맞지 않는다.&lt;br&gt;② 2.1 [vol%] 는 프로판의 하한값이다.&lt;br&gt;④ 4.8 [vol%] 도 맞지 않는다.</t>
+          <t>① 1.6 [vol%]는 계산과 맞지 않는다.&lt;br&gt;② 2.1 [vol%]는 프로판의 하한값이다.&lt;br&gt;④ 4.8 [vol%] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI102" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;르 샤틀리에의 혼합가스 폭발범위&lt;/strong&gt;&lt;br&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$ 다. 답은 언제나 &lt;strong&gt;가장 낮은 하한과 가장 높은 하한 사이&lt;/strong&gt;에 든다. 여기서도 2.1 과 5.0 사이인 3.4 가 나왔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;몫을 더한 뒤 뒤집는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;르 샤틀리에의 혼합가스 폭발범위&lt;/strong&gt;&lt;br&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$다. 답은 언제나 &lt;strong&gt;가장 낮은 하한과 가장 높은 하한 사이&lt;/strong&gt;에 든다. 여기서도 2.1과 5.0 사이인 3.4가 나왔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;몫을 더한 뒤 뒤집는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14367,12 +14367,12 @@
       </c>
       <c r="AG103" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;매 제곱미터당 500 [kg] 이상&lt;/strong&gt;의 하중에 견뎌야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;계단의 기준 (규칙 제26조~제30조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매 제곱미터당 500 [kg] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전율 &lt;u&gt;4 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;급유용·보수용 등은 제외&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 3 [m] 를 초과하면 3 [m] 이내마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;너비 1.2 [m] 이상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 1 [m] 이상이면 개방된 쪽에 설치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위쪽 공간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이내에 장애물이 없게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;매 제곱미터당 500 [kg] 이상&lt;/strong&gt;의 하중에 견뎌야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;계단의 기준 (규칙 제26조~제30조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매 제곱미터당 500 [kg] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전율 &lt;u&gt;4 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;급유용·보수용 등은 제외&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 3 [m]를 초과하면 3 [m] 이내마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;너비 1.2 [m] 이상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 1 [m] 이상이면 개방된 쪽에 설치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위쪽 공간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이내에 장애물이 없게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH103" s="32" t="inlineStr">
         <is>
-          <t>① 300 [kg] 은 기준에 못 미친다.&lt;br&gt;② 400 [kg] 도 못 미친다.&lt;br&gt;④ 600 [kg] 은 기준보다 크다.</t>
+          <t>① 300 [kg]은 기준에 못 미친다.&lt;br&gt;② 400 [kg] 도 못 미친다.&lt;br&gt;④ 600 [kg]은 기준보다 크다.</t>
         </is>
       </c>
       <c r="AI103" s="32" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="AH104" s="32" t="inlineStr">
         <is>
-          <t>① 2 [m] 라는 기준은 없다.&lt;br&gt;② 4 [m] 도 없다.&lt;br&gt;④ 9 [m] 도 없다.</t>
+          <t>① 2 [m]라는 기준은 없다.&lt;br&gt;② 4 [m] 도 없다.&lt;br&gt;④ 9 [m] 도 없다.</t>
         </is>
       </c>
       <c r="AI104" s="32" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="AH105" s="32" t="inlineStr">
         <is>
-          <t>① 50 [kgf] 는 어느 칸에도 없다.&lt;br&gt;② 100 [kgf] 도 없다.&lt;br&gt;④ 200 [kgf] 는 10 [cm] 매듭 있는 방망의 신품 값이다.</t>
+          <t>① 50 [kgf]는 어느 칸에도 없다.&lt;br&gt;② 100 [kgf] 도 없다.&lt;br&gt;④ 200 [kgf]는 10 [cm] 매듭 있는 방망의 신품 값이다.</t>
         </is>
       </c>
       <c r="AI105" s="32" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="AI106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제23조 — 가설통로의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;15 와 10 이 짝, 8 과 7 이 짝&lt;/strong&gt;이다. 숫자를 짝으로 묶어 두면 뒤바꾼 보기를 바로 잡아낸다. &lt;strong&gt;경사 30° 이하, 15° 초과 시 미끄럼 방지&lt;/strong&gt;도 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수직갱 15 → 10, 비계다리 8 → 7&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C23%EC%A1%B0" target="_blank"&gt;제23조(가설통로의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 가설통로를 설치하는 경우 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 견고한 구조로 할 것&lt;br&gt; 2. 경사는 30도 이하로 할 것. 다만, 계단을 설치하거나 높이 2미터 미만의 가설통로로서 튼튼한 손잡이를 설치한 경우에는 그러하지 아니하다.&lt;br&gt; 3. 경사가 15도를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것&lt;br&gt; 4. 추락할 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업상 부득이한 경우에는 필요한 부분만 임시로 해체할 수 있다.&lt;br&gt;▶  5. &lt;strong&gt;수직갱에 가설된 통로의 길이가&lt;/strong&gt; 15미터 이상인 경우에는 10미터 이내마다 계단참을 설치할 것&lt;br&gt; 6. 건설공사에 사용하는 높이 8미터 이상인 비계다리에는 7미터 이내마다 계단참을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제23조 — 가설통로의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;15와 10이 짝, 8과 7이 짝&lt;/strong&gt;이다. 숫자를 짝으로 묶어 두면 뒤바꾼 보기를 바로 잡아낸다. &lt;strong&gt;경사 30° 이하, 15° 초과 시 미끄럼 방지&lt;/strong&gt;도 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수직갱 15 → 10, 비계다리 8 → 7&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C23%EC%A1%B0" target="_blank"&gt;제23조(가설통로의 구조)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 가설통로를 설치하는 경우 다음 각 호의 사항을 준수하여야 한다.&lt;br&gt; 1. 견고한 구조로 할 것&lt;br&gt; 2. 경사는 30도 이하로 할 것. 다만, 계단을 설치하거나 높이 2미터 미만의 가설통로로서 튼튼한 손잡이를 설치한 경우에는 그러하지 아니하다.&lt;br&gt; 3. 경사가 15도를 초과하는 경우에는 미끄러지지 아니하는 구조로 할 것&lt;br&gt; 4. 추락할 위험이 있는 장소에는 안전난간을 설치할 것. 다만, 작업상 부득이한 경우에는 필요한 부분만 임시로 해체할 수 있다.&lt;br&gt;▶  5. &lt;strong&gt;수직갱에 가설된 통로의 길이가&lt;/strong&gt; 15미터 이상인 경우에는 10미터 이내마다 계단참을 설치할 것&lt;br&gt; 6. 건설공사에 사용하는 높이 8미터 이상인 비계다리에는 7미터 이내마다 계단참을 설치할 것&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="AG112" s="32" t="inlineStr">
         <is>
-          <t>간극비는 $e = \dfrac{\text{간극의 부피}}{\text{흙 입자의 부피}} = \dfrac{V_{v}}{V_{s}}$ 다. 간극은 &lt;strong&gt;공기 + 물&lt;/strong&gt;이고, 분모는 &lt;strong&gt;흙 입자만&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;흙의 기본 성질&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용어&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;간극비 e&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{공기} + \text{물}}{\text{흙}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분모가 흙 입자&lt;/u&gt; — 1을 넘을 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;간극률 n&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{공기} + \text{물}}{\text{공기} + \text{흙} + \text{물}} \times 100$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분모가 전체&lt;/u&gt; — 100 [%] 를 넘지 못한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;포화도 S&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{물}}{\text{공기} + \text{물}} \times 100$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;간극 가운데 물이 찬 비율&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;함수비 w&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{물의 무게}}{\text{흙 입자의 무게}} \times 100$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부피가 아니라 무게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>간극비는 $e = \dfrac{\text{간극의 부피}}{\text{흙 입자의 부피}} = \dfrac{V_{v}}{V_{s}}$다. 간극은 &lt;strong&gt;공기 + 물&lt;/strong&gt;이고, 분모는 &lt;strong&gt;흙 입자만&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;흙의 기본 성질&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용어&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;간극비 e&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{공기} + \text{물}}{\text{흙}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분모가 흙 입자&lt;/u&gt; — 1을 넘을 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;간극률 n&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{공기} + \text{물}}{\text{공기} + \text{흙} + \text{물}} \times 100$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분모가 전체&lt;/u&gt; — 100 [%]를 넘지 못한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;포화도 S&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{물}}{\text{공기} + \text{물}} \times 100$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;간극 가운데 물이 찬 비율&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;함수비 w&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{물의 무게}}{\text{흙 입자의 무게}} \times 100$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부피가 아니라 무게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH112" s="32" t="inlineStr">
@@ -15636,7 +15636,7 @@
       <c r="Y113" s="32" t="inlineStr"/>
       <c r="Z113" s="32" t="inlineStr">
         <is>
-          <t>절토, 개착, 터널구간은 기반암의 심도 5~6m 까지 확인한다.</t>
+          <t>절토, 개착, 터널구간은 기반암의 심도 5~6m까지 확인한다.</t>
         </is>
       </c>
       <c r="AA113" s="32" t="inlineStr"/>
@@ -15657,7 +15657,7 @@
       </c>
       <c r="AG113" s="32" t="inlineStr">
         <is>
-          <t>절토·개착·터널 구간은 &lt;strong&gt;기반암의 심도 2 ~ 3 [m] 까지&lt;/strong&gt; 확인한다. 5~6 [m] 가 아니다.</t>
+          <t>절토·개착·터널 구간은 &lt;strong&gt;기반암의 심도 2 ~ 3 [m]까지&lt;/strong&gt; 확인한다. 5~6 [m]가 아니다.</t>
         </is>
       </c>
       <c r="AH113" s="32" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="AG114" s="32" t="inlineStr">
         <is>
-          <t>상부 난간대가 &lt;strong&gt;120 [cm] 를 넘으면 중간 난간대를 2단 이상&lt;/strong&gt; 균등하게 설치한다. 이때 난간대 사이 간격은 &lt;strong&gt;60 [cm] 이하&lt;/strong&gt; 여야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;상부 난간대 높이에 따른 중간 난간대&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상부 난간대 높이&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;중간 난간대&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;90 [cm] 이상 120 [cm] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1단&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;상부와 바닥의 중간에&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;120 [cm] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2단 이상 균등하게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;난간대 사이 60 [cm] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>상부 난간대가 &lt;strong&gt;120 [cm]를 넘으면 중간 난간대를 2단 이상&lt;/strong&gt; 균등하게 설치한다. 이때 난간대 사이 간격은 &lt;strong&gt;60 [cm] 이하&lt;/strong&gt; 여야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;상부 난간대 높이에 따른 중간 난간대&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상부 난간대 높이&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;중간 난간대&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;90 [cm] 이상 120 [cm] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1단&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;상부와 바닥의 중간에&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;120 [cm] 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2단 이상 균등하게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;난간대 사이 60 [cm] 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH114" s="32" t="inlineStr">
@@ -15915,7 +15915,7 @@
       </c>
       <c r="AG115" s="32" t="inlineStr">
         <is>
-          <t>길이 10 [m] 이상이면 &lt;strong&gt;5 [m] 이내마다&lt;/strong&gt; 계단참을 둔다. 3 [m] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;사다리식 통로의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업발판 40 과 다르다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발판과 벽 사이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;발이 들어갈 틈&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발판의 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일정하게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상단 돌출&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;붙잡을 곳&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길이 10 [m] 이상이면 5 [m] 이내마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기울기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고정식은 90° 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>길이 10 [m] 이상이면 &lt;strong&gt;5 [m] 이내마다&lt;/strong&gt; 계단참을 둔다. 3 [m]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;사다리식 통로의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;작업발판 40과 다르다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발판과 벽 사이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;발이 들어갈 틈&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발판의 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일정하게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상단 돌출&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;붙잡을 곳&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길이 10 [m] 이상이면 5 [m] 이내마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기울기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;75° 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고정식은 90° 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH115" s="32" t="inlineStr">
@@ -16552,7 +16552,7 @@
       </c>
       <c r="AG120" s="32" t="inlineStr">
         <is>
-          <t>팽창제의 천공간격은 &lt;strong&gt;30 ~ 70 [cm]&lt;/strong&gt;다. 70~120 [cm] 는 너무 멀어 콘크리트가 갈라지지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;해체용 기계기구의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기구&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;팽창제&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;천공간격 30 ~ 70 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구멍 지름 30 ~ 50 [mm]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;쐐기타입기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;천공구멍이 삽입부 직경과 거의 같게&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화염방사기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;용기 내 온도 40 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;철제해머&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;경험 많은 선임자가 결속&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>팽창제의 천공간격은 &lt;strong&gt;30 ~ 70 [cm]&lt;/strong&gt;다. 70~120 [cm]는 너무 멀어 콘크리트가 갈라지지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;해체용 기계기구의 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기구&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비고&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;팽창제&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;천공간격 30 ~ 70 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구멍 지름 30 ~ 50 [mm]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;쐐기타입기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;천공구멍이 삽입부 직경과 거의 같게&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화염방사기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;용기 내 온도 40 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;철제해머&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;경험 많은 선임자가 결속&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH120" s="32" t="inlineStr">
